--- a/juego_de_pruebas/05_infactible_sin_historico.xlsx
+++ b/juego_de_pruebas/05_infactible_sin_historico.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planificado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Planificado" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,42 +421,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Tren</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Fecha_Ini</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Definición de turno</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Cntd Plan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cntd JDA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Hora Ini</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Secuencia</t>
         </is>
@@ -483,7 +471,7 @@
       <c r="B2" t="n">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>46167</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -515,7 +503,7 @@
       <c r="B3" t="n">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>46167</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -547,7 +535,7 @@
       <c r="B4" t="n">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>46167</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -579,7 +567,7 @@
       <c r="B5" t="n">
         <v>14</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -611,7 +599,7 @@
       <c r="B6" t="n">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="1" t="n">
         <v>46169</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -643,7 +631,7 @@
       <c r="B7" t="n">
         <v>14</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="1" t="n">
         <v>46169</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -675,7 +663,7 @@
       <c r="B8" t="n">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="1" t="n">
         <v>46170</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -707,7 +695,7 @@
       <c r="B9" t="n">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -739,7 +727,7 @@
       <c r="B10" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -771,7 +759,7 @@
       <c r="B11" t="n">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="1" t="n">
         <v>46172</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -803,7 +791,7 @@
       <c r="B12" t="n">
         <v>17</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="1" t="n">
         <v>46167</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -835,7 +823,7 @@
       <c r="B13" t="n">
         <v>17</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="1" t="n">
         <v>46167</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -867,7 +855,7 @@
       <c r="B14" t="n">
         <v>17</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="1" t="n">
         <v>46167</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -899,7 +887,7 @@
       <c r="B15" t="n">
         <v>17</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -931,7 +919,7 @@
       <c r="B16" t="n">
         <v>17</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -963,7 +951,7 @@
       <c r="B17" t="n">
         <v>17</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="1" t="n">
         <v>46169</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -995,7 +983,7 @@
       <c r="B18" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="1" t="n">
         <v>46170</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1027,7 +1015,7 @@
       <c r="B19" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="1" t="n">
         <v>46170</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -1059,7 +1047,7 @@
       <c r="B20" t="n">
         <v>17</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -1091,7 +1079,7 @@
       <c r="B21" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="1" t="n">
         <v>46172</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -1123,7 +1111,7 @@
       <c r="B22" t="n">
         <v>19</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="1" t="n">
         <v>46167</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -1155,7 +1143,7 @@
       <c r="B23" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="1" t="n">
         <v>46167</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -1187,7 +1175,7 @@
       <c r="B24" t="n">
         <v>19</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -1219,7 +1207,7 @@
       <c r="B25" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -1251,7 +1239,7 @@
       <c r="B26" t="n">
         <v>19</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="1" t="n">
         <v>46169</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -1283,7 +1271,7 @@
       <c r="B27" t="n">
         <v>19</v>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="1" t="n">
         <v>46169</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -1315,7 +1303,7 @@
       <c r="B28" t="n">
         <v>19</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="1" t="n">
         <v>46170</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -1347,7 +1335,7 @@
       <c r="B29" t="n">
         <v>19</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="1" t="n">
         <v>46170</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -1379,7 +1367,7 @@
       <c r="B30" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -1411,7 +1399,7 @@
       <c r="B31" t="n">
         <v>19</v>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -1443,7 +1431,7 @@
       <c r="B32" t="n">
         <v>19</v>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="1" t="n">
         <v>46172</v>
       </c>
       <c r="D32" t="inlineStr">
